--- a/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -836,57 +836,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -953,47 +953,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1066,57 +1066,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1183,47 +1183,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,57 +1296,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,47 +1413,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1526,57 +1526,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1706,7 +1706,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1874,47 +1874,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1987,57 +1987,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2104,47 +2104,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2217,57 +2217,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2334,47 +2334,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2447,57 +2447,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2564,47 +2564,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2677,57 +2677,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2857,7 +2857,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3025,47 +3025,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3138,57 +3138,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3255,47 +3255,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3368,57 +3368,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3485,47 +3485,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3598,57 +3598,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3715,47 +3715,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3828,57 +3828,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4008,7 +4008,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4176,64 +4176,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -4289,57 +4289,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4364,17 +4364,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4406,64 +4406,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>432448</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>516619</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -4519,57 +4519,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4594,17 +4594,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4636,64 +4636,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>183349</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -4749,57 +4749,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4866,64 +4866,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>629182</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>761972</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -4979,57 +4979,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5054,17 +5054,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
